--- a/rtm.xlsx
+++ b/rtm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djjun\OneDrive\Documentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8759382-3F7A-4230-9ECF-918910D38219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47ED51DF-DB92-4EA8-88C9-C5DDD95E774F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DBB6952A-4FCA-4DAE-A3D7-7E73E47C7591}"/>
   </bookViews>
@@ -210,7 +210,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -218,17 +218,336 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -239,6 +558,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B0E912AC-9B08-42EB-A6C7-0487A33E8BBF}" name="Tabla2" displayName="Tabla2" ref="A1:G23" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+  <autoFilter ref="A1:G23" xr:uid="{B0E912AC-9B08-42EB-A6C7-0487A33E8BBF}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{9246D6E1-5598-4DB3-8605-4898BF805385}" name="Requirement ID" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{6676D7A8-20B8-484F-A55C-A932A14F61DC}" name="Requirement Description" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{52E84444-1FFB-4050-8AE0-4FE6B0D8C50F}" name="Priority" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{275F68BC-7A7B-4A38-8456-D05E2DCF6FBD}" name="Test Case IDs" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{432696E7-0EE4-4E04-860A-572B81AF7A5F}" name="Coverage" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{FD00284A-E1C8-4540-9DCE-4DFBCFBD57A0}" name="Execution Status" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{34CA837B-3A1E-4719-82F3-FF65148383FE}" name="Defect IDs" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -538,415 +873,468 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{723E263E-812D-47DD-8E90-7A9FB27DD9BF}">
-  <dimension ref="A1:G23"/>
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="41.28515625" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
     <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="C12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="C13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="C14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="C15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="C16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="C17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="C18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="C19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="C20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="C21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="C22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
+      <c r="C23" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>